--- a/src/doc/Libros.xlsx
+++ b/src/doc/Libros.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\book\src\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Github\biblia\src\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E9C83C-2552-4ABB-8536-5DBE98A813CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0722100-C37E-4A4F-A246-8C00D890E7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{D41DDD63-1BD4-4C74-A59C-588FE0709382}"/>
   </bookViews>
@@ -11708,13 +11708,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="40% - Accent4" xfId="1" builtinId="43"/>
@@ -16902,10 +16902,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="30"/>
+      <c r="C2" s="31"/>
     </row>
     <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
@@ -17052,44 +17052,44 @@
       <c r="C23" s="14"/>
     </row>
     <row r="25" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="31" t="str">
+      <c r="B25" s="32" t="str">
         <f>_xlfn.CONCAT(B7," | ",C7)</f>
         <v>1ra. Lectura | Genesis 3,1-7</v>
       </c>
-      <c r="C25" s="31"/>
+      <c r="C25" s="32"/>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
     </row>
     <row r="27" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="str">
+      <c r="B27" s="32" t="str">
         <f>_xlfn.CONCAT(B11," | ",C11)</f>
         <v>2ra. Lectura | Isaías 53,6-10</v>
       </c>
-      <c r="C27" s="31"/>
+      <c r="C27" s="32"/>
     </row>
     <row r="28" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="31" t="str">
+      <c r="B29" s="32" t="str">
         <f>_xlfn.CONCAT(B15," | ",C15)</f>
         <v>3ra. Lectura | Filipenses 2,6-11</v>
       </c>
-      <c r="C29" s="31"/>
+      <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B31" s="31" t="str">
+      <c r="B31" s="32" t="str">
         <f>_xlfn.CONCAT(B19," | ",C19)</f>
         <v>Evangelio | Marcos 25,12-15</v>
       </c>
-      <c r="C31" s="31"/>
+      <c r="C31" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -18536,7 +18536,7 @@
         <v>30</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" ref="L15:L78" si="1">_xlfn.CONCAT("""",G15,"-c",H15,"-v",I15:K15,"""," )</f>
+        <f t="shared" ref="L15:L77" si="1">_xlfn.CONCAT("""",G15,"-c",H15,"-v",I15:K15,"""," )</f>
         <v>"23_sal-c104-v30",</v>
       </c>
     </row>
@@ -19782,7 +19782,7 @@
       <c r="F62">
         <v>12</v>
       </c>
-      <c r="L62" s="32" t="str">
+      <c r="L62" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E62,"-v",F62,""":[")</f>
         <v>"01_gn-c1-v12":[</v>
       </c>
@@ -19887,7 +19887,7 @@
       <c r="F66">
         <v>14</v>
       </c>
-      <c r="L66" s="32" t="str">
+      <c r="L66" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E66,"-v",F66,""":[")</f>
         <v>"01_gn-c1-v14":[</v>
       </c>
@@ -20058,7 +20058,7 @@
       <c r="F72">
         <v>16</v>
       </c>
-      <c r="L72" s="32" t="str">
+      <c r="L72" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E72,"-v",F72,""":[")</f>
         <v>"01_gn-c1-v16":[</v>
       </c>
@@ -20140,7 +20140,7 @@
       <c r="F76">
         <v>18</v>
       </c>
-      <c r="L76" s="32" t="str">
+      <c r="L76" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E76,"-v",F76,""":[")</f>
         <v>"01_gn-c1-v18":[</v>
       </c>
@@ -20167,7 +20167,7 @@
       <c r="F78">
         <v>20</v>
       </c>
-      <c r="L78" s="32" t="str">
+      <c r="L78" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E78,"-v",F78,""":[")</f>
         <v>"01_gn-c1-v20":[</v>
       </c>
@@ -20183,7 +20183,7 @@
         <v>25</v>
       </c>
       <c r="L79" t="str">
-        <f t="shared" ref="L79:L142" si="2">_xlfn.CONCAT("""",G79,"-c",H79,"-v",I79:K79,"""," )</f>
+        <f t="shared" ref="L79:L101" si="2">_xlfn.CONCAT("""",G79,"-c",H79,"-v",I79:K79,"""," )</f>
         <v>"51_hch-c17-v25",</v>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
       <c r="F81">
         <v>21</v>
       </c>
-      <c r="L81" s="32" t="str">
+      <c r="L81" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E81,"-v",F81,""":[")</f>
         <v>"01_gn-c1-v21":[</v>
       </c>
@@ -20302,7 +20302,7 @@
       <c r="F87">
         <v>22</v>
       </c>
-      <c r="L87" s="32" t="str">
+      <c r="L87" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E87,"-v",F87,""":[")</f>
         <v>"01_gn-c1-v22":[</v>
       </c>
@@ -20389,7 +20389,7 @@
       <c r="F93">
         <v>24</v>
       </c>
-      <c r="L93" s="32" t="str">
+      <c r="L93" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E93,"-v",F93,""":[")</f>
         <v>"01_gn-c1-v24":[</v>
       </c>
@@ -20482,7 +20482,7 @@
       <c r="F99">
         <v>25</v>
       </c>
-      <c r="L99" s="32" t="str">
+      <c r="L99" s="30" t="str">
         <f>_xlfn.CONCAT("""01_gn-c",E99,"-v",F99,""":[")</f>
         <v>"01_gn-c1-v25":[</v>
       </c>
